--- a/VI sem/Economica IT-company/lab03/Лабораторная_работа_3_Точка_без_с.xlsx
+++ b/VI sem/Economica IT-company/lab03/Лабораторная_работа_3_Точка_без_с.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\БГТУ\VI сем\Экономика IT компании\lab03\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BGTU\VI sem\Economica IT-company\lab03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2FB2C20-865E-4379-85CC-36F2114666C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7DE95C0-D983-410E-8626-494087EA7BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
   <si>
     <t>Показатели</t>
   </si>
@@ -526,6 +526,39 @@
   <si>
     <t>Кромка безопасности, %</t>
   </si>
+  <si>
+    <t>З пост, тыс.руб.</t>
+  </si>
+  <si>
+    <t>В без, шт</t>
+  </si>
+  <si>
+    <t>З пер, руб/шт</t>
+  </si>
+  <si>
+    <t>Ц, руб/шт</t>
+  </si>
+  <si>
+    <t>Выпуск ф, шт</t>
+  </si>
+  <si>
+    <t>Объем производства, шт</t>
+  </si>
+  <si>
+    <t>Зпост, тыс руб</t>
+  </si>
+  <si>
+    <t>Зпер, тыс руб</t>
+  </si>
+  <si>
+    <t>Зитого</t>
+  </si>
+  <si>
+    <t>Выручка общ, тыс руб</t>
+  </si>
+  <si>
+    <t>Прибыль, тыс руб</t>
+  </si>
 </sst>
 </file>
 
@@ -534,7 +567,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial Cyr"/>
@@ -756,8 +789,14 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial Cyr"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -803,6 +842,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCCFF99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -926,7 +971,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1038,6 +1083,42 @@
     <xf numFmtId="2" fontId="17" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="20" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="20" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="22" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="24" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="29" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1073,7 +1154,2863 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mj-lt"/>
+                <a:ea typeface="+mj-ea"/>
+                <a:cs typeface="+mj-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU" sz="1600" b="1" i="0" u="none" strike="noStrike" normalizeH="0" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>СТРУКТУРА ЗАТРАТ</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mj-lt"/>
+              <a:ea typeface="+mj-ea"/>
+              <a:cs typeface="+mj-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-BY"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="60000"/>
+                      <a:lumOff val="40000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1"/>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-8A99-450F-88AE-AE63696012E0}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="60000"/>
+                      <a:lumOff val="40000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent2"/>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-8A99-450F-88AE-AE63696012E0}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="60000"/>
+                      <a:lumOff val="40000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent3"/>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-8A99-450F-88AE-AE63696012E0}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="60000"/>
+                      <a:lumOff val="40000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent4"/>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-8A99-450F-88AE-AE63696012E0}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="60000"/>
+                      <a:lumOff val="40000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent5"/>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-8A99-450F-88AE-AE63696012E0}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ru-BY"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Исх данные решение'!$A$34:$A$38</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1. Материальные затраты</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2. Фонд оплаты труда работников</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3. Отчисления в ФСЗН</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4. Амортизационные отчисления</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5. Прочие</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Исх данные решение'!$D$34:$D$38</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>52.634400063527352</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.229254347653459</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.5179464782021759</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.0464543794171366</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20.571944731199874</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-0639-4F74-9582-F74E654C6E36}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="70"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredPieSeries>
+              <c15:ser>
+                <c:idx val="0"/>
+                <c:order val="0"/>
+                <c:dPt>
+                  <c:idx val="0"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:gradFill>
+                      <a:gsLst>
+                        <a:gs pos="100000">
+                          <a:schemeClr val="accent1">
+                            <a:lumMod val="60000"/>
+                            <a:lumOff val="40000"/>
+                          </a:schemeClr>
+                        </a:gs>
+                        <a:gs pos="0">
+                          <a:schemeClr val="accent1"/>
+                        </a:gs>
+                      </a:gsLst>
+                      <a:lin ang="5400000" scaled="0"/>
+                    </a:gradFill>
+                    <a:ln w="19050">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:extLst>
+                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                      <c16:uniqueId val="{0000000B-8A99-450F-88AE-AE63696012E0}"/>
+                    </c:ext>
+                  </c:extLst>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="1"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:gradFill>
+                      <a:gsLst>
+                        <a:gs pos="100000">
+                          <a:schemeClr val="accent2">
+                            <a:lumMod val="60000"/>
+                            <a:lumOff val="40000"/>
+                          </a:schemeClr>
+                        </a:gs>
+                        <a:gs pos="0">
+                          <a:schemeClr val="accent2"/>
+                        </a:gs>
+                      </a:gsLst>
+                      <a:lin ang="5400000" scaled="0"/>
+                    </a:gradFill>
+                    <a:ln w="19050">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:extLst>
+                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                      <c16:uniqueId val="{0000000D-8A99-450F-88AE-AE63696012E0}"/>
+                    </c:ext>
+                  </c:extLst>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="2"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:gradFill>
+                      <a:gsLst>
+                        <a:gs pos="100000">
+                          <a:schemeClr val="accent3">
+                            <a:lumMod val="60000"/>
+                            <a:lumOff val="40000"/>
+                          </a:schemeClr>
+                        </a:gs>
+                        <a:gs pos="0">
+                          <a:schemeClr val="accent3"/>
+                        </a:gs>
+                      </a:gsLst>
+                      <a:lin ang="5400000" scaled="0"/>
+                    </a:gradFill>
+                    <a:ln w="19050">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:extLst>
+                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                      <c16:uniqueId val="{0000000F-8A99-450F-88AE-AE63696012E0}"/>
+                    </c:ext>
+                  </c:extLst>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="3"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:gradFill>
+                      <a:gsLst>
+                        <a:gs pos="100000">
+                          <a:schemeClr val="accent4">
+                            <a:lumMod val="60000"/>
+                            <a:lumOff val="40000"/>
+                          </a:schemeClr>
+                        </a:gs>
+                        <a:gs pos="0">
+                          <a:schemeClr val="accent4"/>
+                        </a:gs>
+                      </a:gsLst>
+                      <a:lin ang="5400000" scaled="0"/>
+                    </a:gradFill>
+                    <a:ln w="19050">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:extLst>
+                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                      <c16:uniqueId val="{00000011-8A99-450F-88AE-AE63696012E0}"/>
+                    </c:ext>
+                  </c:extLst>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="4"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:gradFill>
+                      <a:gsLst>
+                        <a:gs pos="100000">
+                          <a:schemeClr val="accent5">
+                            <a:lumMod val="60000"/>
+                            <a:lumOff val="40000"/>
+                          </a:schemeClr>
+                        </a:gs>
+                        <a:gs pos="0">
+                          <a:schemeClr val="accent5"/>
+                        </a:gs>
+                      </a:gsLst>
+                      <a:lin ang="5400000" scaled="0"/>
+                    </a:gradFill>
+                    <a:ln w="19050">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:extLst>
+                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                      <c16:uniqueId val="{00000013-8A99-450F-88AE-AE63696012E0}"/>
+                    </c:ext>
+                  </c:extLst>
+                </c:dPt>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="dk1">
+                              <a:lumMod val="75000"/>
+                              <a:lumOff val="25000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="ru-BY"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="0"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="1"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="1"/>
+                  <c:leaderLines>
+                    <c:spPr>
+                      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                        <a:solidFill>
+                          <a:schemeClr val="dk1">
+                            <a:lumMod val="35000"/>
+                            <a:lumOff val="65000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:round/>
+                      </a:ln>
+                      <a:effectLst/>
+                    </c:spPr>
+                  </c:leaderLines>
+                  <c:extLst>
+                    <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'Исх данные решение'!$A$34:$A$38</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="5"/>
+                      <c:pt idx="0">
+                        <c:v>1. Материальные затраты</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2. Фонд оплаты труда работников</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3. Отчисления в ФСЗН</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>4. Амортизационные отчисления</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>5. Прочие</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'Исх данные решение'!$B$34:$B$38</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="5"/>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000000-0639-4F74-9582-F74E654C6E36}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredPieSeries>
+            <c15:filteredPieSeries>
+              <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="1"/>
+                <c:dPt>
+                  <c:idx val="0"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:gradFill>
+                      <a:gsLst>
+                        <a:gs pos="100000">
+                          <a:schemeClr val="accent1">
+                            <a:lumMod val="60000"/>
+                            <a:lumOff val="40000"/>
+                          </a:schemeClr>
+                        </a:gs>
+                        <a:gs pos="0">
+                          <a:schemeClr val="accent1"/>
+                        </a:gs>
+                      </a:gsLst>
+                      <a:lin ang="5400000" scaled="0"/>
+                    </a:gradFill>
+                    <a:ln w="19050">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:extLst>
+                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                      <c16:uniqueId val="{00000015-8A99-450F-88AE-AE63696012E0}"/>
+                    </c:ext>
+                  </c:extLst>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="1"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:gradFill>
+                      <a:gsLst>
+                        <a:gs pos="100000">
+                          <a:schemeClr val="accent2">
+                            <a:lumMod val="60000"/>
+                            <a:lumOff val="40000"/>
+                          </a:schemeClr>
+                        </a:gs>
+                        <a:gs pos="0">
+                          <a:schemeClr val="accent2"/>
+                        </a:gs>
+                      </a:gsLst>
+                      <a:lin ang="5400000" scaled="0"/>
+                    </a:gradFill>
+                    <a:ln w="19050">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:extLst>
+                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                      <c16:uniqueId val="{00000017-8A99-450F-88AE-AE63696012E0}"/>
+                    </c:ext>
+                  </c:extLst>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="2"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:gradFill>
+                      <a:gsLst>
+                        <a:gs pos="100000">
+                          <a:schemeClr val="accent3">
+                            <a:lumMod val="60000"/>
+                            <a:lumOff val="40000"/>
+                          </a:schemeClr>
+                        </a:gs>
+                        <a:gs pos="0">
+                          <a:schemeClr val="accent3"/>
+                        </a:gs>
+                      </a:gsLst>
+                      <a:lin ang="5400000" scaled="0"/>
+                    </a:gradFill>
+                    <a:ln w="19050">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:extLst>
+                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                      <c16:uniqueId val="{00000019-8A99-450F-88AE-AE63696012E0}"/>
+                    </c:ext>
+                  </c:extLst>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="3"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:gradFill>
+                      <a:gsLst>
+                        <a:gs pos="100000">
+                          <a:schemeClr val="accent4">
+                            <a:lumMod val="60000"/>
+                            <a:lumOff val="40000"/>
+                          </a:schemeClr>
+                        </a:gs>
+                        <a:gs pos="0">
+                          <a:schemeClr val="accent4"/>
+                        </a:gs>
+                      </a:gsLst>
+                      <a:lin ang="5400000" scaled="0"/>
+                    </a:gradFill>
+                    <a:ln w="19050">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:extLst>
+                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                      <c16:uniqueId val="{0000001B-8A99-450F-88AE-AE63696012E0}"/>
+                    </c:ext>
+                  </c:extLst>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="4"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:gradFill>
+                      <a:gsLst>
+                        <a:gs pos="100000">
+                          <a:schemeClr val="accent5">
+                            <a:lumMod val="60000"/>
+                            <a:lumOff val="40000"/>
+                          </a:schemeClr>
+                        </a:gs>
+                        <a:gs pos="0">
+                          <a:schemeClr val="accent5"/>
+                        </a:gs>
+                      </a:gsLst>
+                      <a:lin ang="5400000" scaled="0"/>
+                    </a:gradFill>
+                    <a:ln w="19050">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:extLst>
+                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                      <c16:uniqueId val="{0000001D-8A99-450F-88AE-AE63696012E0}"/>
+                    </c:ext>
+                  </c:extLst>
+                </c:dPt>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="dk1">
+                              <a:lumMod val="75000"/>
+                              <a:lumOff val="25000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="ru-BY"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="0"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="1"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="1"/>
+                  <c:leaderLines>
+                    <c:spPr>
+                      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                        <a:solidFill>
+                          <a:schemeClr val="dk1">
+                            <a:lumMod val="35000"/>
+                            <a:lumOff val="65000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:round/>
+                      </a:ln>
+                      <a:effectLst/>
+                    </c:spPr>
+                  </c:leaderLines>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'Исх данные решение'!$A$34:$A$38</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="5"/>
+                      <c:pt idx="0">
+                        <c:v>1. Материальные затраты</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2. Фонд оплаты труда работников</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3. Отчисления в ФСЗН</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>4. Амортизационные отчисления</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>5. Прочие</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'Исх данные решение'!$C$34:$C$38</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="5"/>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-0639-4F74-9582-F74E654C6E36}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredPieSeries>
+          </c:ext>
+        </c:extLst>
+      </c:doughnutChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-BY"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:pattFill prst="dkDnDiag">
+      <a:fgClr>
+        <a:schemeClr val="lt1"/>
+      </a:fgClr>
+      <a:bgClr>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="10000"/>
+          <a:lumOff val="90000"/>
+        </a:schemeClr>
+      </a:bgClr>
+    </a:pattFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-BY"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Точка</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0"/>
+              <a:t> безубыточности, шт</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-BY"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Исх данные решение'!$F$66</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Зитого</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="35000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent1">
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Исх данные решение'!$E$67:$E$81</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>5229.2222222222217</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7843.833333333333</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10066.707843270338</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10458.444444444443</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>13073.055555555557</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15687.666666666666</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18302.277777777777</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>20916.888888888887</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>23531.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>26146.111111111113</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>28760.722222222219</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>31375.333333333332</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>33989.944444444445</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>36604.555555555555</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>37650.400000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Исх данные решение'!$F$67:$F$81</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>7876.4222222222215</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10491.033333333333</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12713.907843270339</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13105.644444444442</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15720.255555555555</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>18334.866666666665</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20949.477777777778</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>23564.088888888888</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>26178.7</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>28793.311111111114</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>31407.92222222222</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>34022.533333333333</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>36637.144444444442</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>39251.755555555552</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>40297.599999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8FFB-4751-B186-27C2B89610FE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Исх данные решение'!$G$66</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Выручка общ, тыс руб</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="35000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent2">
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent2">
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent2">
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Исх данные решение'!$E$67:$E$81</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>5229.2222222222217</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7843.833333333333</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10066.707843270338</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10458.444444444443</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>13073.055555555557</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15687.666666666666</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18302.277777777777</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>20916.888888888887</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>23531.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>26146.111111111113</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>28760.722222222219</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>31375.333333333332</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>33989.944444444445</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>36604.555555555555</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>37650.400000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Исх данные решение'!$G$67:$G$81</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>6604.3288888888892</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9906.4933333333338</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12713.907843270339</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13208.657777777778</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16510.822222222221</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>19812.986666666668</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>23115.15111111111</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>26417.315555555557</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>29719.48</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>33021.644444444442</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>36323.808888888889</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>39625.973333333335</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>42928.137777777774</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46230.302222222221</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>47551.167999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8FFB-4751-B186-27C2B89610FE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="643482920"/>
+        <c:axId val="643483280"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="643482920"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-BY"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="643483280"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="643483280"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-BY"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="643482920"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-BY"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-BY"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="256">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="dkDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="lt1"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="10000"/>
+            <a:lumOff val="90000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:alpha val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="0"/>
+      </a:gradFill>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="0"/>
+      </a:gradFill>
+      <a:ln w="50800">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="15875">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="800" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:alpha val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="major">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="0" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="343">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>282389</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>165847</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>461683</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>13447</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Диаграмма 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>443754</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>255494</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>237565</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>112059</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="11" name="Диаграмма 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -1240,7 +4177,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1711,13 +4648,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:L81"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
     <col min="2" max="2" width="8.109375" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="8.77734375" customWidth="1"/>
     <col min="6" max="6" width="8.21875" customWidth="1"/>
     <col min="7" max="7" width="8.77734375" customWidth="1"/>
@@ -1727,39 +4664,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" ht="90.3" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="70" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
     </row>
     <row r="2" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="69"/>
     </row>
     <row r="3" spans="1:11" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A3" s="46"/>
+      <c r="A3" s="66"/>
       <c r="B3" s="8">
         <v>1</v>
       </c>
@@ -1801,7 +4738,7 @@
       <c r="C4" s="10">
         <v>60000</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="45">
         <v>72000</v>
       </c>
       <c r="E4" s="10">
@@ -1836,7 +4773,7 @@
       <c r="C5" s="10">
         <v>220</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="45">
         <v>240</v>
       </c>
       <c r="E5" s="10">
@@ -1871,7 +4808,7 @@
       <c r="C6" s="10">
         <v>80</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="45">
         <v>140</v>
       </c>
       <c r="E6" s="10">
@@ -1906,7 +4843,7 @@
       <c r="C7" s="10">
         <v>0.37</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="45">
         <v>0.38</v>
       </c>
       <c r="E7" s="10">
@@ -1941,7 +4878,7 @@
       <c r="C8" s="11">
         <v>95</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="46">
         <v>90</v>
       </c>
       <c r="E8" s="11">
@@ -1976,7 +4913,7 @@
       <c r="C9" s="11">
         <v>65</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="46">
         <v>60</v>
       </c>
       <c r="E9" s="11">
@@ -2011,7 +4948,7 @@
       <c r="C10" s="11">
         <v>3840</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="46">
         <v>5460</v>
       </c>
       <c r="E10" s="11">
@@ -2046,7 +4983,7 @@
       <c r="C11" s="11">
         <v>18350</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="46">
         <v>19960</v>
       </c>
       <c r="E11" s="11">
@@ -2081,7 +5018,7 @@
       <c r="C12" s="11">
         <v>12</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="46">
         <v>8</v>
       </c>
       <c r="E12" s="11">
@@ -2116,7 +5053,7 @@
       <c r="C13" s="11">
         <v>5500</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="46">
         <v>6000</v>
       </c>
       <c r="E13" s="11">
@@ -2151,7 +5088,7 @@
       <c r="C14" s="11">
         <v>2100</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="46">
         <v>1700</v>
       </c>
       <c r="E14" s="11">
@@ -2186,7 +5123,7 @@
       <c r="C15" s="11">
         <v>180</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="46">
         <v>150</v>
       </c>
       <c r="E15" s="11">
@@ -2221,7 +5158,7 @@
       <c r="C16" s="11">
         <v>650</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="46">
         <v>220</v>
       </c>
       <c r="E16" s="11">
@@ -2256,7 +5193,7 @@
       <c r="C17" s="11">
         <v>110</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="46">
         <v>160</v>
       </c>
       <c r="E17" s="11">
@@ -2291,7 +5228,7 @@
       <c r="C18" s="11">
         <v>95</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="46">
         <v>100</v>
       </c>
       <c r="E18" s="11">
@@ -2326,7 +5263,7 @@
       <c r="C19" s="11">
         <v>50</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="46">
         <v>60</v>
       </c>
       <c r="E19" s="11">
@@ -2361,7 +5298,7 @@
       <c r="C20" s="10">
         <v>12</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="45">
         <v>18</v>
       </c>
       <c r="E20" s="10">
@@ -2407,9 +5344,9 @@
       </c>
       <c r="B22" s="24"/>
       <c r="C22" s="24"/>
-      <c r="D22" s="24">
-        <f>D5*D4+D6*D7*D4+D18</f>
-        <v>21110500</v>
+      <c r="D22" s="47">
+        <f>D5*D4+D6*D7*D4+D18*1000</f>
+        <v>21210400</v>
       </c>
       <c r="E22" s="24"/>
       <c r="F22" s="24"/>
@@ -2426,8 +5363,8 @@
       <c r="B23" s="25"/>
       <c r="C23" s="25"/>
       <c r="D23" s="25">
-        <f>(D8*D4)+D9</f>
-        <v>6480060</v>
+        <f>(D8*D4)+D9*1000</f>
+        <v>6540000</v>
       </c>
       <c r="E23" s="25"/>
       <c r="F23" s="25"/>
@@ -2445,7 +5382,7 @@
       <c r="C24" s="25"/>
       <c r="D24" s="25">
         <f>D23*0.34</f>
-        <v>2203220.4000000004</v>
+        <v>2223600</v>
       </c>
       <c r="E24" s="25"/>
       <c r="F24" s="25"/>
@@ -2462,8 +5399,8 @@
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25">
-        <f>(D10+D11)*D12/100</f>
-        <v>2033.6</v>
+        <f>((D10+D11)*D12/100)*1000</f>
+        <v>2033600</v>
       </c>
       <c r="E25" s="25"/>
       <c r="F25" s="25"/>
@@ -2480,8 +5417,8 @@
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25">
-        <f>D13+D14+D15+D16+D17+D19</f>
-        <v>8290</v>
+        <f>(D13+D14+D15+D16+D17+D19)*1000</f>
+        <v>8290000</v>
       </c>
       <c r="E26" s="25"/>
       <c r="F26" s="25"/>
@@ -2499,7 +5436,7 @@
       <c r="C27" s="26"/>
       <c r="D27" s="26">
         <f>SUM(D22:D26)</f>
-        <v>29804104</v>
+        <v>40297600</v>
       </c>
       <c r="E27" s="26"/>
       <c r="F27" s="26"/>
@@ -2515,7 +5452,10 @@
       </c>
       <c r="B28" s="27"/>
       <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
+      <c r="D28" s="49">
+        <f>D27/D4</f>
+        <v>559.68888888888887</v>
+      </c>
       <c r="E28" s="27"/>
       <c r="F28" s="27"/>
       <c r="G28" s="27"/>
@@ -2530,7 +5470,10 @@
       </c>
       <c r="B29" s="28"/>
       <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
+      <c r="D29" s="48">
+        <f>D28*D20/100+D28</f>
+        <v>660.4328888888889</v>
+      </c>
       <c r="E29" s="28"/>
       <c r="F29" s="28"/>
       <c r="G29" s="28"/>
@@ -2563,7 +5506,10 @@
       </c>
       <c r="B31" s="29"/>
       <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
+      <c r="D31" s="29">
+        <f>(D27-D30*1000)/D4</f>
+        <v>522.92222222222222</v>
+      </c>
       <c r="E31" s="29"/>
       <c r="F31" s="29"/>
       <c r="G31" s="29"/>
@@ -2578,7 +5524,10 @@
       </c>
       <c r="B32" s="19"/>
       <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
+      <c r="D32" s="19">
+        <f>D30*1000/(D29-D31)</f>
+        <v>19250.870235521121</v>
+      </c>
       <c r="E32" s="19"/>
       <c r="F32" s="19"/>
       <c r="G32" s="19"/>
@@ -2587,7 +5536,7 @@
       <c r="J32" s="19"/>
       <c r="K32" s="19"/>
     </row>
-    <row r="33" spans="1:11" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A33" s="20" t="s">
         <v>24</v>
       </c>
@@ -2602,13 +5551,16 @@
       <c r="J33" s="21"/>
       <c r="K33" s="21"/>
     </row>
-    <row r="34" spans="1:11" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A34" s="32" t="s">
         <v>11</v>
       </c>
       <c r="B34" s="22"/>
       <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
+      <c r="D34" s="50">
+        <f>(D22/$D$27*100)</f>
+        <v>52.634400063527352</v>
+      </c>
       <c r="E34" s="22"/>
       <c r="F34" s="22"/>
       <c r="G34" s="22"/>
@@ -2617,13 +5569,16 @@
       <c r="J34" s="22"/>
       <c r="K34" s="22"/>
     </row>
-    <row r="35" spans="1:11" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="32" t="s">
         <v>12</v>
       </c>
       <c r="B35" s="23"/>
       <c r="C35" s="23"/>
-      <c r="D35" s="23"/>
+      <c r="D35" s="50">
+        <f t="shared" ref="D35:D38" si="0">(D23/$D$27*100)</f>
+        <v>16.229254347653459</v>
+      </c>
       <c r="E35" s="23"/>
       <c r="F35" s="23"/>
       <c r="G35" s="23"/>
@@ -2632,13 +5587,16 @@
       <c r="J35" s="23"/>
       <c r="K35" s="23"/>
     </row>
-    <row r="36" spans="1:11" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="32" t="s">
         <v>10</v>
       </c>
       <c r="B36" s="23"/>
       <c r="C36" s="23"/>
-      <c r="D36" s="23"/>
+      <c r="D36" s="50">
+        <f t="shared" si="0"/>
+        <v>5.5179464782021759</v>
+      </c>
       <c r="E36" s="23"/>
       <c r="F36" s="23"/>
       <c r="G36" s="23"/>
@@ -2647,13 +5605,16 @@
       <c r="J36" s="23"/>
       <c r="K36" s="23"/>
     </row>
-    <row r="37" spans="1:11" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="32" t="s">
         <v>13</v>
       </c>
       <c r="B37" s="23"/>
       <c r="C37" s="23"/>
-      <c r="D37" s="23"/>
+      <c r="D37" s="50">
+        <f t="shared" si="0"/>
+        <v>5.0464543794171366</v>
+      </c>
       <c r="E37" s="23"/>
       <c r="F37" s="23"/>
       <c r="G37" s="23"/>
@@ -2662,13 +5623,16 @@
       <c r="J37" s="23"/>
       <c r="K37" s="23"/>
     </row>
-    <row r="38" spans="1:11" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="32" t="s">
         <v>14</v>
       </c>
       <c r="B38" s="23"/>
       <c r="C38" s="23"/>
-      <c r="D38" s="23"/>
+      <c r="D38" s="50">
+        <f t="shared" si="0"/>
+        <v>20.571944731199874</v>
+      </c>
       <c r="E38" s="23"/>
       <c r="F38" s="23"/>
       <c r="G38" s="23"/>
@@ -2677,13 +5641,16 @@
       <c r="J38" s="23"/>
       <c r="K38" s="23"/>
     </row>
-    <row r="39" spans="1:11" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="17" t="s">
         <v>15</v>
       </c>
       <c r="B39" s="30"/>
       <c r="C39" s="30"/>
-      <c r="D39" s="30"/>
+      <c r="D39" s="51">
+        <f>SUM(D34:D38)</f>
+        <v>100.00000000000001</v>
+      </c>
       <c r="E39" s="30"/>
       <c r="F39" s="30"/>
       <c r="G39" s="30"/>
@@ -2692,7 +5659,7 @@
       <c r="J39" s="30"/>
       <c r="K39" s="30"/>
     </row>
-    <row r="40" spans="1:11" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A40" s="44" t="s">
         <v>64</v>
       </c>
@@ -2707,7 +5674,7 @@
       <c r="J40" s="43"/>
       <c r="K40" s="43"/>
     </row>
-    <row r="41" spans="1:11" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A41" s="44" t="s">
         <v>65</v>
       </c>
@@ -2722,6 +5689,531 @@
       <c r="J41" s="43"/>
       <c r="K41" s="43"/>
     </row>
+    <row r="45" spans="1:12" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D45" s="57" t="s">
+        <v>66</v>
+      </c>
+      <c r="E45" s="58">
+        <f>D30</f>
+        <v>2647.2</v>
+      </c>
+      <c r="G45" s="54"/>
+      <c r="H45" s="54"/>
+      <c r="I45" s="54"/>
+      <c r="J45" s="54"/>
+      <c r="K45" s="54"/>
+      <c r="L45" s="54"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D46" s="57" t="s">
+        <v>68</v>
+      </c>
+      <c r="E46" s="58">
+        <f>D31</f>
+        <v>522.92222222222222</v>
+      </c>
+      <c r="H46" s="52"/>
+      <c r="I46" s="52"/>
+      <c r="J46" s="52"/>
+      <c r="L46" s="52"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D47" s="57" t="s">
+        <v>67</v>
+      </c>
+      <c r="E47" s="59">
+        <f>D32</f>
+        <v>19250.870235521121</v>
+      </c>
+      <c r="H47" s="52"/>
+      <c r="I47" s="52"/>
+      <c r="J47" s="52"/>
+      <c r="L47" s="52"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D48" s="57" t="s">
+        <v>69</v>
+      </c>
+      <c r="E48" s="60">
+        <f>D29</f>
+        <v>660.4328888888889</v>
+      </c>
+      <c r="G48" s="53"/>
+      <c r="H48" s="52"/>
+      <c r="I48" s="52"/>
+      <c r="J48" s="52"/>
+      <c r="L48" s="52"/>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="D49" s="57" t="s">
+        <v>70</v>
+      </c>
+      <c r="E49" s="57">
+        <f>D4</f>
+        <v>72000</v>
+      </c>
+      <c r="H49" s="52"/>
+      <c r="I49" s="55"/>
+      <c r="J49" s="55"/>
+      <c r="K49" s="56"/>
+      <c r="L49" s="55"/>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="H50" s="52"/>
+      <c r="I50" s="52"/>
+      <c r="J50" s="52"/>
+      <c r="L50" s="52"/>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="H51" s="52"/>
+      <c r="I51" s="52"/>
+      <c r="J51" s="52"/>
+      <c r="L51" s="52"/>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="H52" s="52"/>
+      <c r="I52" s="52"/>
+      <c r="J52" s="52"/>
+      <c r="L52" s="52"/>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="G53" s="53"/>
+      <c r="H53" s="52"/>
+      <c r="I53" s="52"/>
+      <c r="J53" s="52"/>
+      <c r="L53" s="52"/>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="H54" s="52"/>
+      <c r="I54" s="52"/>
+      <c r="J54" s="52"/>
+      <c r="L54" s="52"/>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="H55" s="52"/>
+      <c r="I55" s="52"/>
+      <c r="J55" s="52"/>
+      <c r="L55" s="52"/>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="H56" s="52"/>
+      <c r="I56" s="52"/>
+      <c r="J56" s="52"/>
+      <c r="L56" s="52"/>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="H57" s="52"/>
+      <c r="I57" s="55"/>
+      <c r="J57" s="55"/>
+      <c r="K57" s="56"/>
+      <c r="L57" s="55"/>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="H58" s="52"/>
+    </row>
+    <row r="59" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="H59" s="52"/>
+    </row>
+    <row r="60" spans="4:12" x14ac:dyDescent="0.25">
+      <c r="H60" s="52"/>
+    </row>
+    <row r="66" spans="3:8" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="C66" s="61" t="s">
+        <v>71</v>
+      </c>
+      <c r="D66" s="61" t="s">
+        <v>72</v>
+      </c>
+      <c r="E66" s="61" t="s">
+        <v>73</v>
+      </c>
+      <c r="F66" s="61" t="s">
+        <v>74</v>
+      </c>
+      <c r="G66" s="61" t="s">
+        <v>75</v>
+      </c>
+      <c r="H66" s="61" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="67" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C67" s="57">
+        <v>10000</v>
+      </c>
+      <c r="D67" s="58">
+        <f t="shared" ref="D67:D81" si="1">$E$45</f>
+        <v>2647.2</v>
+      </c>
+      <c r="E67" s="58">
+        <f>$E$46*C67/1000</f>
+        <v>5229.2222222222217</v>
+      </c>
+      <c r="F67" s="58">
+        <f>D67+E67</f>
+        <v>7876.4222222222215</v>
+      </c>
+      <c r="G67" s="57">
+        <f>$E$48*C67/1000</f>
+        <v>6604.3288888888892</v>
+      </c>
+      <c r="H67" s="58">
+        <f>G67-F67</f>
+        <v>-1272.0933333333323</v>
+      </c>
+    </row>
+    <row r="68" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C68" s="57">
+        <v>15000</v>
+      </c>
+      <c r="D68" s="58">
+        <f t="shared" si="1"/>
+        <v>2647.2</v>
+      </c>
+      <c r="E68" s="58">
+        <f t="shared" ref="E68:E81" si="2">$E$46*C68/1000</f>
+        <v>7843.833333333333</v>
+      </c>
+      <c r="F68" s="58">
+        <f t="shared" ref="F68:F81" si="3">D68+E68</f>
+        <v>10491.033333333333</v>
+      </c>
+      <c r="G68" s="57">
+        <f t="shared" ref="G68:G81" si="4">$E$48*C68/1000</f>
+        <v>9906.4933333333338</v>
+      </c>
+      <c r="H68" s="58">
+        <f t="shared" ref="H68:H81" si="5">G68-F68</f>
+        <v>-584.53999999999905</v>
+      </c>
+    </row>
+    <row r="69" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C69" s="62">
+        <f>E47</f>
+        <v>19250.870235521121</v>
+      </c>
+      <c r="D69" s="63">
+        <f>$E$45</f>
+        <v>2647.2</v>
+      </c>
+      <c r="E69" s="63">
+        <f t="shared" si="2"/>
+        <v>10066.707843270338</v>
+      </c>
+      <c r="F69" s="63">
+        <f t="shared" si="3"/>
+        <v>12713.907843270339</v>
+      </c>
+      <c r="G69" s="64">
+        <f t="shared" si="4"/>
+        <v>12713.907843270339</v>
+      </c>
+      <c r="H69" s="63">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C70" s="57">
+        <v>20000</v>
+      </c>
+      <c r="D70" s="58">
+        <f t="shared" si="1"/>
+        <v>2647.2</v>
+      </c>
+      <c r="E70" s="58">
+        <f t="shared" si="2"/>
+        <v>10458.444444444443</v>
+      </c>
+      <c r="F70" s="58">
+        <f t="shared" si="3"/>
+        <v>13105.644444444442</v>
+      </c>
+      <c r="G70" s="57">
+        <f t="shared" si="4"/>
+        <v>13208.657777777778</v>
+      </c>
+      <c r="H70" s="58">
+        <f t="shared" si="5"/>
+        <v>103.01333333333605</v>
+      </c>
+    </row>
+    <row r="71" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C71" s="57">
+        <v>25000</v>
+      </c>
+      <c r="D71" s="58">
+        <f t="shared" si="1"/>
+        <v>2647.2</v>
+      </c>
+      <c r="E71" s="58">
+        <f t="shared" si="2"/>
+        <v>13073.055555555557</v>
+      </c>
+      <c r="F71" s="58">
+        <f t="shared" si="3"/>
+        <v>15720.255555555555</v>
+      </c>
+      <c r="G71" s="57">
+        <f t="shared" si="4"/>
+        <v>16510.822222222221</v>
+      </c>
+      <c r="H71" s="58">
+        <f t="shared" si="5"/>
+        <v>790.5666666666657</v>
+      </c>
+    </row>
+    <row r="72" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C72" s="57">
+        <v>30000</v>
+      </c>
+      <c r="D72" s="58">
+        <f t="shared" si="1"/>
+        <v>2647.2</v>
+      </c>
+      <c r="E72" s="58">
+        <f t="shared" si="2"/>
+        <v>15687.666666666666</v>
+      </c>
+      <c r="F72" s="58">
+        <f t="shared" si="3"/>
+        <v>18334.866666666665</v>
+      </c>
+      <c r="G72" s="57">
+        <f t="shared" si="4"/>
+        <v>19812.986666666668</v>
+      </c>
+      <c r="H72" s="58">
+        <f t="shared" si="5"/>
+        <v>1478.1200000000026</v>
+      </c>
+    </row>
+    <row r="73" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C73" s="57">
+        <v>35000</v>
+      </c>
+      <c r="D73" s="58">
+        <f t="shared" si="1"/>
+        <v>2647.2</v>
+      </c>
+      <c r="E73" s="58">
+        <f t="shared" si="2"/>
+        <v>18302.277777777777</v>
+      </c>
+      <c r="F73" s="58">
+        <f t="shared" si="3"/>
+        <v>20949.477777777778</v>
+      </c>
+      <c r="G73" s="57">
+        <f t="shared" si="4"/>
+        <v>23115.15111111111</v>
+      </c>
+      <c r="H73" s="58">
+        <f t="shared" si="5"/>
+        <v>2165.6733333333323</v>
+      </c>
+    </row>
+    <row r="74" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C74" s="59">
+        <v>40000</v>
+      </c>
+      <c r="D74" s="58">
+        <f t="shared" si="1"/>
+        <v>2647.2</v>
+      </c>
+      <c r="E74" s="58">
+        <f t="shared" si="2"/>
+        <v>20916.888888888887</v>
+      </c>
+      <c r="F74" s="58">
+        <f t="shared" si="3"/>
+        <v>23564.088888888888</v>
+      </c>
+      <c r="G74" s="57">
+        <f t="shared" si="4"/>
+        <v>26417.315555555557</v>
+      </c>
+      <c r="H74" s="58">
+        <f t="shared" si="5"/>
+        <v>2853.2266666666692</v>
+      </c>
+    </row>
+    <row r="75" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C75" s="57">
+        <v>45000</v>
+      </c>
+      <c r="D75" s="58">
+        <f t="shared" si="1"/>
+        <v>2647.2</v>
+      </c>
+      <c r="E75" s="58">
+        <f t="shared" si="2"/>
+        <v>23531.5</v>
+      </c>
+      <c r="F75" s="58">
+        <f t="shared" si="3"/>
+        <v>26178.7</v>
+      </c>
+      <c r="G75" s="57">
+        <f t="shared" si="4"/>
+        <v>29719.48</v>
+      </c>
+      <c r="H75" s="58">
+        <f t="shared" si="5"/>
+        <v>3540.7799999999988</v>
+      </c>
+    </row>
+    <row r="76" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C76" s="57">
+        <v>50000</v>
+      </c>
+      <c r="D76" s="58">
+        <f t="shared" si="1"/>
+        <v>2647.2</v>
+      </c>
+      <c r="E76" s="58">
+        <f t="shared" si="2"/>
+        <v>26146.111111111113</v>
+      </c>
+      <c r="F76" s="58">
+        <f t="shared" si="3"/>
+        <v>28793.311111111114</v>
+      </c>
+      <c r="G76" s="57">
+        <f t="shared" si="4"/>
+        <v>33021.644444444442</v>
+      </c>
+      <c r="H76" s="58">
+        <f t="shared" si="5"/>
+        <v>4228.3333333333285</v>
+      </c>
+    </row>
+    <row r="77" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C77" s="57">
+        <v>55000</v>
+      </c>
+      <c r="D77" s="58">
+        <f t="shared" si="1"/>
+        <v>2647.2</v>
+      </c>
+      <c r="E77" s="58">
+        <f t="shared" si="2"/>
+        <v>28760.722222222219</v>
+      </c>
+      <c r="F77" s="58">
+        <f t="shared" si="3"/>
+        <v>31407.92222222222</v>
+      </c>
+      <c r="G77" s="57">
+        <f t="shared" si="4"/>
+        <v>36323.808888888889</v>
+      </c>
+      <c r="H77" s="58">
+        <f t="shared" si="5"/>
+        <v>4915.886666666669</v>
+      </c>
+    </row>
+    <row r="78" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C78" s="57">
+        <v>60000</v>
+      </c>
+      <c r="D78" s="58">
+        <f t="shared" si="1"/>
+        <v>2647.2</v>
+      </c>
+      <c r="E78" s="58">
+        <f t="shared" si="2"/>
+        <v>31375.333333333332</v>
+      </c>
+      <c r="F78" s="58">
+        <f t="shared" si="3"/>
+        <v>34022.533333333333</v>
+      </c>
+      <c r="G78" s="57">
+        <f t="shared" si="4"/>
+        <v>39625.973333333335</v>
+      </c>
+      <c r="H78" s="58">
+        <f t="shared" si="5"/>
+        <v>5603.4400000000023</v>
+      </c>
+    </row>
+    <row r="79" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C79" s="57">
+        <v>65000</v>
+      </c>
+      <c r="D79" s="58">
+        <f t="shared" si="1"/>
+        <v>2647.2</v>
+      </c>
+      <c r="E79" s="58">
+        <f t="shared" si="2"/>
+        <v>33989.944444444445</v>
+      </c>
+      <c r="F79" s="58">
+        <f t="shared" si="3"/>
+        <v>36637.144444444442</v>
+      </c>
+      <c r="G79" s="57">
+        <f t="shared" si="4"/>
+        <v>42928.137777777774</v>
+      </c>
+      <c r="H79" s="58">
+        <f t="shared" si="5"/>
+        <v>6290.993333333332</v>
+      </c>
+    </row>
+    <row r="80" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C80" s="57">
+        <v>70000</v>
+      </c>
+      <c r="D80" s="58">
+        <f t="shared" si="1"/>
+        <v>2647.2</v>
+      </c>
+      <c r="E80" s="58">
+        <f t="shared" si="2"/>
+        <v>36604.555555555555</v>
+      </c>
+      <c r="F80" s="58">
+        <f t="shared" si="3"/>
+        <v>39251.755555555552</v>
+      </c>
+      <c r="G80" s="57">
+        <f t="shared" si="4"/>
+        <v>46230.302222222221</v>
+      </c>
+      <c r="H80" s="58">
+        <f t="shared" si="5"/>
+        <v>6978.5466666666689</v>
+      </c>
+    </row>
+    <row r="81" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C81" s="64">
+        <f>E49</f>
+        <v>72000</v>
+      </c>
+      <c r="D81" s="63">
+        <f t="shared" si="1"/>
+        <v>2647.2</v>
+      </c>
+      <c r="E81" s="63">
+        <f t="shared" si="2"/>
+        <v>37650.400000000001</v>
+      </c>
+      <c r="F81" s="63">
+        <f t="shared" si="3"/>
+        <v>40297.599999999999</v>
+      </c>
+      <c r="G81" s="64">
+        <f t="shared" si="4"/>
+        <v>47551.167999999998</v>
+      </c>
+      <c r="H81" s="63">
+        <f t="shared" si="5"/>
+        <v>7253.5679999999993</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:A3"/>
@@ -2732,6 +6224,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
